--- a/3dpack1.xlsx
+++ b/3dpack1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6efecc3210076de/Desktop/Acad/MTP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="196" documentId="8_{264CFC6C-0552-4E79-AC5E-12A4E536DF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40318935-48CF-4D53-98CF-D4B719C95649}"/>
+  <xr:revisionPtr revIDLastSave="208" documentId="8_{264CFC6C-0552-4E79-AC5E-12A4E536DF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB3593CA-2FAB-456E-AD51-7D2E6D60EA4A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{48667665-2070-4B77-AF56-5C458F011BCB}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{48667665-2070-4B77-AF56-5C458F011BCB}"/>
   </bookViews>
   <sheets>
     <sheet name="SKU" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{006BDADF-01D5-4C94-B959-14B47C9BA51E}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -553,6 +553,23 @@
       </c>
       <c r="E7">
         <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -562,7 +579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECFAED6D-E511-434C-804E-F193708C4E45}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.88671875" customWidth="1"/>
@@ -628,6 +645,26 @@
         <v>4</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
